--- a/data/사모_260612.xlsx
+++ b/data/사모_260612.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>3,907</t>
+          <t>3,883</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>49,276</t>
+          <t>48,761</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>145,246</t>
+          <t>144,707</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="R11" s="10" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>-539</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>13,514</t>
+          <t>12,975</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R12" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>714</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>714</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="R26" s="10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>30,459</t>
+          <t>30,469</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
-          <t>51,278</t>
+          <t>51,288</t>
         </is>
       </c>
       <c r="Q28" s="10" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="R28" s="10" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>10,200</t>
+          <t>10,210</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>4,041</t>
+          <t>4,047</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>4,579</t>
+          <t>4,588</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>-715</t>
+          <t>-705</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>4,264</t>
+          <t>4,250</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>36,154</t>
+          <t>35,332</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>52,039</t>
+          <t>51,204</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-836</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>13,068</t>
+          <t>12,232</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>5,128</t>
+          <t>5,108</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>6,892</t>
+          <t>6,872</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="R37" s="10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>1,734</t>
+          <t>1,714</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="R38" s="10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>717</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>41,532</t>
+          <t>41,006</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>1,324</t>
+          <t>1,314</t>
         </is>
       </c>
       <c r="N47" s="10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>49,752</t>
+          <t>49,193</t>
         </is>
       </c>
       <c r="Q47" s="10" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="R47" s="10" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-559</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>1,140</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>12,314</t>
+          <t>12,964</t>
         </is>
       </c>
       <c r="N48" s="10" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>14,058</t>
+          <t>14,708</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="R48" s="10" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>650</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>4,323</t>
+          <t>4,973</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>852</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>2,406</t>
+          <t>2,497</t>
         </is>
       </c>
       <c r="Q56" s="10" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="R56" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>-580</t>
+          <t>-488</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
-          <t>18,264</t>
+          <t>19,617</t>
         </is>
       </c>
       <c r="N58" s="10" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>24,742</t>
+          <t>26,095</t>
         </is>
       </c>
       <c r="Q58" s="10" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="R58" s="10" t="inlineStr">
         <is>
-          <t>-174</t>
+          <t>1,353</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>6,401</t>
+          <t>7,754</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>304</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P61" s="10" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Q61" s="10" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="R61" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="R62" s="10" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>1,938</t>
+          <t>1,937</t>
         </is>
       </c>
       <c r="Q65" s="10" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="R65" s="10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="R76" s="10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S76" s="10" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>746</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="P80" s="10" t="inlineStr">
         <is>
-          <t>1,193</t>
+          <t>1,333</t>
         </is>
       </c>
       <c r="Q80" s="10" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="R80" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S80" s="10" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>8,346</t>
+          <t>8,362</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>99,522</t>
+          <t>98,504</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P85" s="10" t="inlineStr">
         <is>
-          <t>112,753</t>
+          <t>112,751</t>
         </is>
       </c>
       <c r="Q85" s="10" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>-55</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="S85" s="10" t="inlineStr">
         <is>
-          <t>7,377</t>
+          <t>7,375</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>2,444</t>
         </is>
       </c>
       <c r="N91" s="10" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="P91" s="10" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>2,444</t>
         </is>
       </c>
       <c r="Q91" s="10" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="R91" s="10" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="S91" s="10" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>663</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="R95" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S95" s="10" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>4,766</t>
+          <t>4,812</t>
         </is>
       </c>
       <c r="K98" s="10" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="P98" s="10" t="inlineStr">
         <is>
-          <t>5,645</t>
+          <t>5,691</t>
         </is>
       </c>
       <c r="Q98" s="10" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="R98" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="S98" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>581</t>
         </is>
       </c>
       <c r="N104" s="10" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="P104" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>581</t>
         </is>
       </c>
       <c r="Q104" s="10" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="R104" s="10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="S104" s="10" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>11,865</t>
+          <t>11,871</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>75,699</t>
+          <t>75,698</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>382,543</t>
+          <t>380,830</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>15,186</t>
+          <t>14,696</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>32,230</t>
+          <t>32,228</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="P105" s="10" t="inlineStr">
         <is>
-          <t>593,076</t>
+          <t>590,877</t>
         </is>
       </c>
       <c r="Q105" s="10" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="R105" s="10" t="inlineStr">
         <is>
-          <t>-12,458</t>
+          <t>-2,198</t>
         </is>
       </c>
       <c r="S105" s="10" t="inlineStr">
         <is>
-          <t>100,642</t>
+          <t>98,444</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,854</t>
         </is>
       </c>
       <c r="N108" s="10" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="P108" s="10" t="inlineStr">
         <is>
-          <t>2,489</t>
+          <t>2,842</t>
         </is>
       </c>
       <c r="Q108" s="10" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="R108" s="10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>353</t>
         </is>
       </c>
       <c r="S108" s="10" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>658</t>
         </is>
       </c>
       <c r="N110" s="10" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P110" s="10" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Q110" s="10" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="R110" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S110" s="10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>3,489</t>
+          <t>3,492</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="P114" s="10" t="inlineStr">
         <is>
-          <t>4,229</t>
+          <t>3,842</t>
         </is>
       </c>
       <c r="Q114" s="10" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="R114" s="10" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>-387</t>
         </is>
       </c>
       <c r="S114" s="10" t="inlineStr">
         <is>
-          <t>-2,249</t>
+          <t>-2,636</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>3,912</t>
+          <t>3,915</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P117" s="10" t="inlineStr">
         <is>
-          <t>5,906</t>
+          <t>5,909</t>
         </is>
       </c>
       <c r="Q117" s="10" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="R117" s="10" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S117" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>519</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>3,195</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>4,232</t>
+          <t>4,237</t>
         </is>
       </c>
       <c r="Q121" s="10" t="inlineStr">
@@ -11858,12 +11858,12 @@
       </c>
       <c r="R121" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S121" s="10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>2,786</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>63,221</t>
+          <t>63,223</t>
         </is>
       </c>
       <c r="Q124" s="10" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="R124" s="10" t="inlineStr">
         <is>
-          <t>1,059</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S124" s="10" t="inlineStr">
         <is>
-          <t>6,568</t>
+          <t>6,570</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>8,818</t>
+          <t>8,815</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>10,737</t>
+          <t>10,733</t>
         </is>
       </c>
       <c r="Q125" s="10" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="R125" s="10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="S125" s="10" t="inlineStr">
         <is>
-          <t>-1,093</t>
+          <t>-1,097</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>1,538</t>
+          <t>1,536</t>
         </is>
       </c>
       <c r="Q128" s="10" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="R128" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="S128" s="10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>1,529</t>
+          <t>1,530</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="R129" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S129" s="10" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="P131" s="10" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>746</t>
         </is>
       </c>
       <c r="Q131" s="10" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="R131" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S131" s="10" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
     </row>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="R132" s="10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S132" s="10" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>4,609</t>
+          <t>4,611</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>25,763</t>
+          <t>24,735</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>1,918</t>
+          <t>1,932</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>35,794</t>
+          <t>34,782</t>
         </is>
       </c>
       <c r="Q137" s="10" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="R137" s="10" t="inlineStr">
         <is>
-          <t>-79</t>
+          <t>-1,012</t>
         </is>
       </c>
       <c r="S137" s="10" t="inlineStr">
         <is>
-          <t>-11,937</t>
+          <t>-12,950</t>
         </is>
       </c>
     </row>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="R139" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S139" s="10" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>239</t>
         </is>
       </c>
       <c r="N140" s="10" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="P140" s="10" t="inlineStr">
         <is>
-          <t>2,289</t>
+          <t>2,390</t>
         </is>
       </c>
       <c r="Q140" s="10" t="inlineStr">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="R140" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="S140" s="10" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="J142" s="10" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>466</t>
         </is>
       </c>
       <c r="K142" s="10" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="P142" s="10" t="inlineStr">
         <is>
-          <t>1,696</t>
+          <t>1,652</t>
         </is>
       </c>
       <c r="Q142" s="10" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="R142" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="S142" s="10" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>715</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="R145" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S145" s="10" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="J146" s="10" t="inlineStr">
         <is>
-          <t>75,987</t>
+          <t>76,061</t>
         </is>
       </c>
       <c r="K146" s="10" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="P146" s="10" t="inlineStr">
         <is>
-          <t>75,987</t>
+          <t>76,061</t>
         </is>
       </c>
       <c r="Q146" s="10" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="R146" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="S146" s="10" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>512</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>111,742</t>
+          <t>111,722</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>611,228</t>
+          <t>619,694</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="P147" s="10" t="inlineStr">
         <is>
-          <t>804,142</t>
+          <t>812,589</t>
         </is>
       </c>
       <c r="Q147" s="10" t="inlineStr">
@@ -14380,12 +14380,12 @@
       </c>
       <c r="R147" s="10" t="inlineStr">
         <is>
-          <t>8,818</t>
+          <t>8,446</t>
         </is>
       </c>
       <c r="S147" s="10" t="inlineStr">
         <is>
-          <t>151,349</t>
+          <t>159,795</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>577</t>
         </is>
       </c>
       <c r="N152" s="10" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="P152" s="10" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>908</t>
         </is>
       </c>
       <c r="Q152" s="10" t="inlineStr">
@@ -14865,12 +14865,12 @@
       </c>
       <c r="R152" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="S152" s="10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="R154" s="10" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S154" s="10" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="R161" s="10" t="inlineStr">
         <is>
-          <t>-144</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S161" s="10" t="inlineStr">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="R165" s="10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S165" s="10" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>1,941</t>
+          <t>1,944</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="P176" s="10" t="inlineStr">
         <is>
-          <t>2,875</t>
+          <t>2,878</t>
         </is>
       </c>
       <c r="Q176" s="10" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="R176" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S176" s="10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="R177" s="10" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S177" s="10" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
-          <t>36,596</t>
+          <t>36,593</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="J182" s="10" t="inlineStr">
         <is>
-          <t>17,721</t>
+          <t>17,783</t>
         </is>
       </c>
       <c r="K182" s="10" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="M182" s="10" t="inlineStr">
         <is>
-          <t>43,771</t>
+          <t>44,110</t>
         </is>
       </c>
       <c r="N182" s="10" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P182" s="10" t="inlineStr">
         <is>
-          <t>214,444</t>
+          <t>214,842</t>
         </is>
       </c>
       <c r="Q182" s="10" t="inlineStr">
@@ -17775,12 +17775,12 @@
       </c>
       <c r="R182" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>398</t>
         </is>
       </c>
       <c r="S182" s="10" t="inlineStr">
         <is>
-          <t>12,334</t>
+          <t>12,732</t>
         </is>
       </c>
     </row>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="M187" s="10" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>923</t>
         </is>
       </c>
       <c r="N187" s="10" t="inlineStr">
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P187" s="10" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>923</t>
         </is>
       </c>
       <c r="Q187" s="10" t="inlineStr">
@@ -18260,12 +18260,12 @@
       </c>
       <c r="R187" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S187" s="10" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>555</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="P191" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Q191" s="10" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="R191" s="10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="S191" s="10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -19951,12 +19951,12 @@
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
-          <t>114,294</t>
+          <t>114,794</t>
         </is>
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>58,426</t>
+          <t>56,928</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="P205" s="10" t="inlineStr">
         <is>
-          <t>210,943</t>
+          <t>209,944</t>
         </is>
       </c>
       <c r="Q205" s="10" t="inlineStr">
@@ -20006,12 +20006,12 @@
       </c>
       <c r="R205" s="10" t="inlineStr">
         <is>
-          <t>1,547</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="S205" s="10" t="inlineStr">
         <is>
-          <t>26,389</t>
+          <t>25,391</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>1,045</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="E208" s="10" t="inlineStr">
         <is>
-          <t>21,626</t>
+          <t>21,587</t>
         </is>
       </c>
       <c r="F208" s="10" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="P208" s="10" t="inlineStr">
         <is>
-          <t>49,780</t>
+          <t>49,696</t>
         </is>
       </c>
       <c r="Q208" s="10" t="inlineStr">
@@ -20297,12 +20297,12 @@
       </c>
       <c r="R208" s="10" t="inlineStr">
         <is>
-          <t>-54</t>
+          <t>-83</t>
         </is>
       </c>
       <c r="S208" s="10" t="inlineStr">
         <is>
-          <t>8,340</t>
+          <t>8,257</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>1,263</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P212" s="10" t="inlineStr">
         <is>
-          <t>1,450</t>
+          <t>1,476</t>
         </is>
       </c>
       <c r="Q212" s="10" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="R212" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S212" s="10" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="R218" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S218" s="10" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>922</t>
         </is>
       </c>
       <c r="N220" s="10" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="P220" s="10" t="inlineStr">
         <is>
-          <t>2,755</t>
+          <t>2,860</t>
         </is>
       </c>
       <c r="Q220" s="10" t="inlineStr">
@@ -21461,12 +21461,12 @@
       </c>
       <c r="R220" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="S220" s="10" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -21478,7 +21478,7 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="P221" s="10" t="inlineStr">
         <is>
-          <t>4,148</t>
+          <t>4,151</t>
         </is>
       </c>
       <c r="Q221" s="10" t="inlineStr">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="S221" s="10" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-129</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="M231" s="10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>266</t>
         </is>
       </c>
       <c r="N231" s="10" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="P231" s="10" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>559</t>
         </is>
       </c>
       <c r="Q231" s="10" t="inlineStr">
@@ -22528,12 +22528,12 @@
       </c>
       <c r="R231" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="S231" s="10" t="inlineStr">
         <is>
-          <t>-48</t>
+          <t>-51</t>
         </is>
       </c>
     </row>
@@ -23473,7 +23473,7 @@
       </c>
       <c r="M241" s="10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N241" s="10" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="P241" s="10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Q241" s="10" t="inlineStr">
@@ -23498,12 +23498,12 @@
       </c>
       <c r="R241" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S241" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -24371,7 +24371,7 @@
       </c>
       <c r="R250" s="10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S250" s="10" t="inlineStr">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="R257" s="10" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S257" s="10" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="R260" s="10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S260" s="10" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="R271" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S271" s="10" t="inlineStr">
@@ -26577,7 +26577,7 @@
       </c>
       <c r="M273" s="10" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>753</t>
         </is>
       </c>
       <c r="N273" s="10" t="inlineStr">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="P273" s="10" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>753</t>
         </is>
       </c>
       <c r="Q273" s="10" t="inlineStr">
@@ -26602,12 +26602,12 @@
       </c>
       <c r="R273" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S273" s="10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>9,774</t>
+          <t>9,751</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -26828,7 +26828,7 @@
       </c>
       <c r="E276" s="10" t="inlineStr">
         <is>
-          <t>90,478</t>
+          <t>90,387</t>
         </is>
       </c>
       <c r="F276" s="10" t="inlineStr">
@@ -26883,7 +26883,7 @@
       </c>
       <c r="P276" s="10" t="inlineStr">
         <is>
-          <t>209,358</t>
+          <t>209,245</t>
         </is>
       </c>
       <c r="Q276" s="10" t="inlineStr">
@@ -26893,12 +26893,12 @@
       </c>
       <c r="R276" s="10" t="inlineStr">
         <is>
-          <t>1,110</t>
+          <t>-113</t>
         </is>
       </c>
       <c r="S276" s="10" t="inlineStr">
         <is>
-          <t>6,650</t>
+          <t>6,536</t>
         </is>
       </c>
     </row>
@@ -26990,7 +26990,7 @@
       </c>
       <c r="R277" s="10" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S277" s="10" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="M281" s="10" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>914</t>
         </is>
       </c>
       <c r="N281" s="10" t="inlineStr">
@@ -27368,7 +27368,7 @@
       </c>
       <c r="P281" s="10" t="inlineStr">
         <is>
-          <t>1,301</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="Q281" s="10" t="inlineStr">
@@ -27378,12 +27378,12 @@
       </c>
       <c r="R281" s="10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="S281" s="10" t="inlineStr">
         <is>
-          <t>-101</t>
+          <t>-102</t>
         </is>
       </c>
     </row>
@@ -27475,7 +27475,7 @@
       </c>
       <c r="R282" s="10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S282" s="10" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="R290" s="10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S290" s="10" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="R293" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S293" s="10" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="B299" s="10" t="inlineStr">
         <is>
-          <t>1,134</t>
+          <t>1,138</t>
         </is>
       </c>
       <c r="C299" s="10" t="inlineStr">
@@ -29074,7 +29074,7 @@
       </c>
       <c r="H299" s="10" t="inlineStr">
         <is>
-          <t>71,869</t>
+          <t>70,882</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="L299" s="10" t="inlineStr">
         <is>
-          <t>16,427</t>
+          <t>16,401</t>
         </is>
       </c>
       <c r="M299" s="10" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="P299" s="10" t="inlineStr">
         <is>
-          <t>198,880</t>
+          <t>197,872</t>
         </is>
       </c>
       <c r="Q299" s="10" t="inlineStr">
@@ -29124,12 +29124,12 @@
       </c>
       <c r="R299" s="10" t="inlineStr">
         <is>
-          <t>-2,330</t>
+          <t>-1,008</t>
         </is>
       </c>
       <c r="S299" s="10" t="inlineStr">
         <is>
-          <t>25,369</t>
+          <t>24,361</t>
         </is>
       </c>
     </row>
@@ -29432,7 +29432,7 @@
       </c>
       <c r="B303" s="10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C303" s="10" t="inlineStr">
@@ -29502,7 +29502,7 @@
       </c>
       <c r="P303" s="10" t="inlineStr">
         <is>
-          <t>1,973</t>
+          <t>1,975</t>
         </is>
       </c>
       <c r="Q303" s="10" t="inlineStr">
@@ -29512,12 +29512,12 @@
       </c>
       <c r="R303" s="10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S303" s="10" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -29534,7 +29534,7 @@
       </c>
       <c r="C304" s="10" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>467</t>
         </is>
       </c>
       <c r="D304" s="10" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="P304" s="10" t="inlineStr">
         <is>
-          <t>1,907</t>
+          <t>2,008</t>
         </is>
       </c>
       <c r="Q304" s="10" t="inlineStr">
@@ -29609,12 +29609,12 @@
       </c>
       <c r="R304" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="S304" s="10" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>470</t>
         </is>
       </c>
     </row>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="S307" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="B317" s="10" t="inlineStr">
         <is>
-          <t>8,157</t>
+          <t>8,120</t>
         </is>
       </c>
       <c r="C317" s="10" t="inlineStr">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="P317" s="10" t="inlineStr">
         <is>
-          <t>56,379</t>
+          <t>56,342</t>
         </is>
       </c>
       <c r="Q317" s="10" t="inlineStr">
@@ -30870,12 +30870,12 @@
       </c>
       <c r="R317" s="10" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="S317" s="10" t="inlineStr">
         <is>
-          <t>6,074</t>
+          <t>6,037</t>
         </is>
       </c>
     </row>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="I318" s="10" t="inlineStr">
         <is>
-          <t>2,258</t>
+          <t>1,758</t>
         </is>
       </c>
       <c r="J318" s="10" t="inlineStr">
@@ -30957,7 +30957,7 @@
       </c>
       <c r="P318" s="10" t="inlineStr">
         <is>
-          <t>26,951</t>
+          <t>26,451</t>
         </is>
       </c>
       <c r="Q318" s="10" t="inlineStr">
@@ -30967,12 +30967,12 @@
       </c>
       <c r="R318" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="S318" s="10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>-385</t>
         </is>
       </c>
     </row>
@@ -31161,7 +31161,7 @@
       </c>
       <c r="R320" s="10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S320" s="10" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="R325" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S325" s="10" t="inlineStr">
@@ -32295,7 +32295,7 @@
       </c>
       <c r="L332" s="10" t="inlineStr">
         <is>
-          <t>2,907</t>
+          <t>2,927</t>
         </is>
       </c>
       <c r="M332" s="10" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="P332" s="10" t="inlineStr">
         <is>
-          <t>148,044</t>
+          <t>148,063</t>
         </is>
       </c>
       <c r="Q332" s="10" t="inlineStr">
@@ -32325,12 +32325,12 @@
       </c>
       <c r="R332" s="10" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S332" s="10" t="inlineStr">
         <is>
-          <t>-1,875</t>
+          <t>-1,856</t>
         </is>
       </c>
     </row>
@@ -33877,7 +33877,7 @@
       </c>
       <c r="R348" s="10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S348" s="10" t="inlineStr">
@@ -34071,7 +34071,7 @@
       </c>
       <c r="R350" s="10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S350" s="10" t="inlineStr">
@@ -35138,7 +35138,7 @@
       </c>
       <c r="R361" s="10" t="inlineStr">
         <is>
-          <t>1,950</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S361" s="10" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="S365" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -35640,7 +35640,7 @@
       </c>
       <c r="B367" s="10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C367" s="10" t="inlineStr">
@@ -35710,7 +35710,7 @@
       </c>
       <c r="P367" s="10" t="inlineStr">
         <is>
-          <t>2,534</t>
+          <t>2,540</t>
         </is>
       </c>
       <c r="Q367" s="10" t="inlineStr">
@@ -35720,12 +35720,12 @@
       </c>
       <c r="R367" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S367" s="10" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -35737,7 +35737,7 @@
       </c>
       <c r="B368" s="10" t="inlineStr">
         <is>
-          <t>3,882</t>
+          <t>3,885</t>
         </is>
       </c>
       <c r="C368" s="10" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="P368" s="10" t="inlineStr">
         <is>
-          <t>11,021</t>
+          <t>11,024</t>
         </is>
       </c>
       <c r="Q368" s="10" t="inlineStr">
@@ -35817,12 +35817,12 @@
       </c>
       <c r="R368" s="10" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S368" s="10" t="inlineStr">
         <is>
-          <t>4,070</t>
+          <t>4,073</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="J372" s="10" t="inlineStr">
         <is>
-          <t>14,285</t>
+          <t>14,308</t>
         </is>
       </c>
       <c r="K372" s="10" t="inlineStr">
@@ -36195,7 +36195,7 @@
       </c>
       <c r="P372" s="10" t="inlineStr">
         <is>
-          <t>14,285</t>
+          <t>14,308</t>
         </is>
       </c>
       <c r="Q372" s="10" t="inlineStr">
@@ -36205,12 +36205,12 @@
       </c>
       <c r="R372" s="10" t="inlineStr">
         <is>
-          <t>1,379</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S372" s="10" t="inlineStr">
         <is>
-          <t>1,266</t>
+          <t>1,289</t>
         </is>
       </c>
     </row>
@@ -36416,7 +36416,7 @@
       </c>
       <c r="B375" s="10" t="inlineStr">
         <is>
-          <t>7,300</t>
+          <t>7,254</t>
         </is>
       </c>
       <c r="C375" s="10" t="inlineStr">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D375" s="10" t="inlineStr">
         <is>
-          <t>2,502</t>
+          <t>1,502</t>
         </is>
       </c>
       <c r="E375" s="10" t="inlineStr">
         <is>
-          <t>82,044</t>
+          <t>81,544</t>
         </is>
       </c>
       <c r="F375" s="10" t="inlineStr">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="H375" s="10" t="inlineStr">
         <is>
-          <t>75,496</t>
+          <t>75,198</t>
         </is>
       </c>
       <c r="I375" s="10" t="inlineStr">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="M375" s="10" t="inlineStr">
         <is>
-          <t>14,184</t>
+          <t>14,299</t>
         </is>
       </c>
       <c r="N375" s="10" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="P375" s="10" t="inlineStr">
         <is>
-          <t>302,890</t>
+          <t>301,161</t>
         </is>
       </c>
       <c r="Q375" s="10" t="inlineStr">
@@ -36496,12 +36496,12 @@
       </c>
       <c r="R375" s="10" t="inlineStr">
         <is>
-          <t>1,627</t>
+          <t>-1,729</t>
         </is>
       </c>
       <c r="S375" s="10" t="inlineStr">
         <is>
-          <t>27,733</t>
+          <t>26,004</t>
         </is>
       </c>
     </row>
@@ -36610,7 +36610,7 @@
       </c>
       <c r="B377" s="10" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>927</t>
         </is>
       </c>
       <c r="C377" s="10" t="inlineStr">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="P377" s="10" t="inlineStr">
         <is>
-          <t>5,137</t>
+          <t>5,141</t>
         </is>
       </c>
       <c r="Q377" s="10" t="inlineStr">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="R377" s="10" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S377" s="10" t="inlineStr">
         <is>
-          <t>1,392</t>
+          <t>1,396</t>
         </is>
       </c>
     </row>
@@ -36819,7 +36819,7 @@
       </c>
       <c r="E379" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="F379" s="10" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="M379" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>95</t>
         </is>
       </c>
       <c r="N379" s="10" t="inlineStr">
@@ -36874,7 +36874,7 @@
       </c>
       <c r="P379" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>398</t>
         </is>
       </c>
       <c r="Q379" s="10" t="inlineStr">
@@ -36884,12 +36884,12 @@
       </c>
       <c r="R379" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="S379" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -37197,7 +37197,7 @@
       </c>
       <c r="C383" s="10" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>242</t>
         </is>
       </c>
       <c r="D383" s="10" t="inlineStr">
@@ -37247,7 +37247,7 @@
       </c>
       <c r="M383" s="10" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N383" s="10" t="inlineStr">
@@ -37262,7 +37262,7 @@
       </c>
       <c r="P383" s="10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>415</t>
         </is>
       </c>
       <c r="Q383" s="10" t="inlineStr">
@@ -37272,12 +37272,12 @@
       </c>
       <c r="R383" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="S383" s="10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -37660,7 +37660,7 @@
       </c>
       <c r="R387" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S387" s="10" t="inlineStr">
@@ -38008,7 +38008,7 @@
       </c>
       <c r="J391" s="10" t="inlineStr">
         <is>
-          <t>26,686</t>
+          <t>26,690</t>
         </is>
       </c>
       <c r="K391" s="10" t="inlineStr">
@@ -38038,7 +38038,7 @@
       </c>
       <c r="P391" s="10" t="inlineStr">
         <is>
-          <t>26,686</t>
+          <t>26,690</t>
         </is>
       </c>
       <c r="Q391" s="10" t="inlineStr">
@@ -38048,12 +38048,12 @@
       </c>
       <c r="R391" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S391" s="10" t="inlineStr">
         <is>
-          <t>-172</t>
+          <t>-168</t>
         </is>
       </c>
     </row>
@@ -38242,7 +38242,7 @@
       </c>
       <c r="R393" s="10" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S393" s="10" t="inlineStr">
@@ -38339,7 +38339,7 @@
       </c>
       <c r="R394" s="10" t="inlineStr">
         <is>
-          <t>-54</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S394" s="10" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="B397" s="10" t="inlineStr">
         <is>
-          <t>1,384</t>
+          <t>1,365</t>
         </is>
       </c>
       <c r="C397" s="10" t="inlineStr">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="E397" s="10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F397" s="10" t="inlineStr">
@@ -38605,7 +38605,7 @@
       </c>
       <c r="M397" s="10" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>685</t>
         </is>
       </c>
       <c r="N397" s="10" t="inlineStr">
@@ -38620,7 +38620,7 @@
       </c>
       <c r="P397" s="10" t="inlineStr">
         <is>
-          <t>3,378</t>
+          <t>3,304</t>
         </is>
       </c>
       <c r="Q397" s="10" t="inlineStr">
@@ -38630,12 +38630,12 @@
       </c>
       <c r="R397" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-73</t>
         </is>
       </c>
       <c r="S397" s="10" t="inlineStr">
         <is>
-          <t>-201</t>
+          <t>-274</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="D400" s="10" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E400" s="10" t="inlineStr">
@@ -38896,7 +38896,7 @@
       </c>
       <c r="M400" s="10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>230</t>
         </is>
       </c>
       <c r="N400" s="10" t="inlineStr">
@@ -38911,7 +38911,7 @@
       </c>
       <c r="P400" s="10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Q400" s="10" t="inlineStr">
@@ -38921,12 +38921,12 @@
       </c>
       <c r="R400" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S400" s="10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -39381,7 +39381,7 @@
       </c>
       <c r="M405" s="10" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>755</t>
         </is>
       </c>
       <c r="N405" s="10" t="inlineStr">
@@ -39396,7 +39396,7 @@
       </c>
       <c r="P405" s="10" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Q405" s="10" t="inlineStr">
@@ -39406,12 +39406,12 @@
       </c>
       <c r="R405" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S405" s="10" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="M407" s="10" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>378</t>
         </is>
       </c>
       <c r="N407" s="10" t="inlineStr">
@@ -39590,7 +39590,7 @@
       </c>
       <c r="P407" s="10" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>378</t>
         </is>
       </c>
       <c r="Q407" s="10" t="inlineStr">
@@ -39600,12 +39600,12 @@
       </c>
       <c r="R407" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-43</t>
         </is>
       </c>
       <c r="S407" s="10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="B408" s="10" t="inlineStr">
         <is>
-          <t>7,800</t>
+          <t>7,805</t>
         </is>
       </c>
       <c r="C408" s="10" t="inlineStr">
@@ -39647,7 +39647,7 @@
       </c>
       <c r="H408" s="10" t="inlineStr">
         <is>
-          <t>47,771</t>
+          <t>51,735</t>
         </is>
       </c>
       <c r="I408" s="10" t="inlineStr">
@@ -39687,7 +39687,7 @@
       </c>
       <c r="P408" s="10" t="inlineStr">
         <is>
-          <t>180,335</t>
+          <t>184,303</t>
         </is>
       </c>
       <c r="Q408" s="10" t="inlineStr">
@@ -39697,12 +39697,12 @@
       </c>
       <c r="R408" s="10" t="inlineStr">
         <is>
-          <t>-188</t>
+          <t>3,968</t>
         </is>
       </c>
       <c r="S408" s="10" t="inlineStr">
         <is>
-          <t>-12,332</t>
+          <t>-8,364</t>
         </is>
       </c>
     </row>
@@ -40045,7 +40045,7 @@
       </c>
       <c r="J412" s="10" t="inlineStr">
         <is>
-          <t>2,458</t>
+          <t>2,858</t>
         </is>
       </c>
       <c r="K412" s="10" t="inlineStr">
@@ -40075,7 +40075,7 @@
       </c>
       <c r="P412" s="10" t="inlineStr">
         <is>
-          <t>2,558</t>
+          <t>2,958</t>
         </is>
       </c>
       <c r="Q412" s="10" t="inlineStr">
@@ -40085,12 +40085,12 @@
       </c>
       <c r="R412" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="S412" s="10" t="inlineStr">
         <is>
-          <t>-83</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -40137,7 +40137,7 @@
       </c>
       <c r="I413" s="10" t="inlineStr">
         <is>
-          <t>6,980</t>
+          <t>6,985</t>
         </is>
       </c>
       <c r="J413" s="10" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="P413" s="10" t="inlineStr">
         <is>
-          <t>9,419</t>
+          <t>9,425</t>
         </is>
       </c>
       <c r="Q413" s="10" t="inlineStr">
@@ -40182,12 +40182,12 @@
       </c>
       <c r="R413" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S413" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
     </row>
@@ -40530,7 +40530,7 @@
       </c>
       <c r="J417" s="10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>618</t>
         </is>
       </c>
       <c r="K417" s="10" t="inlineStr">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="P417" s="10" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1,048</t>
         </is>
       </c>
       <c r="Q417" s="10" t="inlineStr">
@@ -40570,12 +40570,12 @@
       </c>
       <c r="R417" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="S417" s="10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -40739,7 +40739,7 @@
       </c>
       <c r="M419" s="10" t="inlineStr">
         <is>
-          <t>1,271</t>
+          <t>1,686</t>
         </is>
       </c>
       <c r="N419" s="10" t="inlineStr">
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P419" s="10" t="inlineStr">
         <is>
-          <t>1,271</t>
+          <t>1,686</t>
         </is>
       </c>
       <c r="Q419" s="10" t="inlineStr">
@@ -40764,12 +40764,12 @@
       </c>
       <c r="R419" s="10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>415</t>
         </is>
       </c>
       <c r="S419" s="10" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1,193</t>
         </is>
       </c>
     </row>
@@ -40958,7 +40958,7 @@
       </c>
       <c r="R421" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S421" s="10" t="inlineStr">
@@ -41363,7 +41363,7 @@
       </c>
       <c r="B426" s="10" t="inlineStr">
         <is>
-          <t>5,497</t>
+          <t>6,123</t>
         </is>
       </c>
       <c r="C426" s="10" t="inlineStr">
@@ -41433,7 +41433,7 @@
       </c>
       <c r="P426" s="10" t="inlineStr">
         <is>
-          <t>12,850</t>
+          <t>13,477</t>
         </is>
       </c>
       <c r="Q426" s="10" t="inlineStr">
@@ -41443,12 +41443,12 @@
       </c>
       <c r="R426" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>626</t>
         </is>
       </c>
       <c r="S426" s="10" t="inlineStr">
         <is>
-          <t>-2,417</t>
+          <t>-1,790</t>
         </is>
       </c>
     </row>
@@ -41612,7 +41612,7 @@
       </c>
       <c r="M428" s="10" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N428" s="10" t="inlineStr">
@@ -41627,7 +41627,7 @@
       </c>
       <c r="P428" s="10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Q428" s="10" t="inlineStr">
@@ -41637,12 +41637,12 @@
       </c>
       <c r="R428" s="10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="S428" s="10" t="inlineStr">
         <is>
-          <t>-38</t>
+          <t>-53</t>
         </is>
       </c>
     </row>
@@ -42144,7 +42144,7 @@
       </c>
       <c r="C434" s="10" t="inlineStr">
         <is>
-          <t>2,187</t>
+          <t>1,615</t>
         </is>
       </c>
       <c r="D434" s="10" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="P434" s="10" t="inlineStr">
         <is>
-          <t>3,721</t>
+          <t>3,149</t>
         </is>
       </c>
       <c r="Q434" s="10" t="inlineStr">
@@ -42219,12 +42219,12 @@
       </c>
       <c r="R434" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-572</t>
         </is>
       </c>
       <c r="S434" s="10" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>-416</t>
         </is>
       </c>
     </row>
@@ -42510,7 +42510,7 @@
       </c>
       <c r="R437" s="10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S437" s="10" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="R439" s="10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S439" s="10" t="inlineStr">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="M447" s="10" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>1,347</t>
         </is>
       </c>
       <c r="N447" s="10" t="inlineStr">
@@ -43470,7 +43470,7 @@
       </c>
       <c r="P447" s="10" t="inlineStr">
         <is>
-          <t>2,510</t>
+          <t>2,507</t>
         </is>
       </c>
       <c r="Q447" s="10" t="inlineStr">
@@ -43480,12 +43480,12 @@
       </c>
       <c r="R447" s="10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="S447" s="10" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>636</t>
         </is>
       </c>
     </row>
@@ -44089,7 +44089,7 @@
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>425</t>
         </is>
       </c>
       <c r="E454" s="10" t="inlineStr">
@@ -44149,7 +44149,7 @@
       </c>
       <c r="P454" s="10" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>944</t>
         </is>
       </c>
       <c r="Q454" s="10" t="inlineStr">
@@ -44159,12 +44159,12 @@
       </c>
       <c r="R454" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S454" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -44303,7 +44303,7 @@
       </c>
       <c r="H456" s="10" t="inlineStr">
         <is>
-          <t>45,594</t>
+          <t>46,590</t>
         </is>
       </c>
       <c r="I456" s="10" t="inlineStr">
@@ -44343,7 +44343,7 @@
       </c>
       <c r="P456" s="10" t="inlineStr">
         <is>
-          <t>50,772</t>
+          <t>51,769</t>
         </is>
       </c>
       <c r="Q456" s="10" t="inlineStr">
@@ -44353,12 +44353,12 @@
       </c>
       <c r="R456" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="S456" s="10" t="inlineStr">
         <is>
-          <t>25,702</t>
+          <t>26,699</t>
         </is>
       </c>
     </row>
@@ -45340,7 +45340,7 @@
       </c>
       <c r="B467" s="10" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>532</t>
         </is>
       </c>
       <c r="C467" s="10" t="inlineStr">
@@ -45355,7 +45355,7 @@
       </c>
       <c r="E467" s="10" t="inlineStr">
         <is>
-          <t>27,137</t>
+          <t>27,138</t>
         </is>
       </c>
       <c r="F467" s="10" t="inlineStr">
@@ -45370,7 +45370,7 @@
       </c>
       <c r="H467" s="10" t="inlineStr">
         <is>
-          <t>92,965</t>
+          <t>100,831</t>
         </is>
       </c>
       <c r="I467" s="10" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="P467" s="10" t="inlineStr">
         <is>
-          <t>123,299</t>
+          <t>131,173</t>
         </is>
       </c>
       <c r="Q467" s="10" t="inlineStr">
@@ -45420,12 +45420,12 @@
       </c>
       <c r="R467" s="10" t="inlineStr">
         <is>
-          <t>-2,263</t>
+          <t>7,873</t>
         </is>
       </c>
       <c r="S467" s="10" t="inlineStr">
         <is>
-          <t>-12,109</t>
+          <t>-4,236</t>
         </is>
       </c>
     </row>
@@ -45589,7 +45589,7 @@
       </c>
       <c r="M469" s="10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N469" s="10" t="inlineStr">
@@ -45604,7 +45604,7 @@
       </c>
       <c r="P469" s="10" t="inlineStr">
         <is>
-          <t>1,307</t>
+          <t>1,319</t>
         </is>
       </c>
       <c r="Q469" s="10" t="inlineStr">
@@ -45614,12 +45614,12 @@
       </c>
       <c r="R469" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S469" s="10" t="inlineStr">
         <is>
-          <t>-234</t>
+          <t>-222</t>
         </is>
       </c>
     </row>
@@ -45711,7 +45711,7 @@
       </c>
       <c r="R470" s="10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S470" s="10" t="inlineStr">
@@ -45875,7 +45875,7 @@
       </c>
       <c r="L472" s="10" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>4,519</t>
         </is>
       </c>
       <c r="M472" s="10" t="inlineStr">
@@ -45895,7 +45895,7 @@
       </c>
       <c r="P472" s="10" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>4,519</t>
         </is>
       </c>
       <c r="Q472" s="10" t="inlineStr">
@@ -45905,12 +45905,12 @@
       </c>
       <c r="R472" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="S472" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -46268,7 +46268,7 @@
       </c>
       <c r="M476" s="10" t="inlineStr">
         <is>
-          <t>53,324</t>
+          <t>53,535</t>
         </is>
       </c>
       <c r="N476" s="10" t="inlineStr">
@@ -46283,7 +46283,7 @@
       </c>
       <c r="P476" s="10" t="inlineStr">
         <is>
-          <t>80,586</t>
+          <t>80,797</t>
         </is>
       </c>
       <c r="Q476" s="10" t="inlineStr">
@@ -46293,12 +46293,12 @@
       </c>
       <c r="R476" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="S476" s="10" t="inlineStr">
         <is>
-          <t>4,071</t>
+          <t>4,281</t>
         </is>
       </c>
     </row>
@@ -46447,7 +46447,7 @@
       </c>
       <c r="J478" s="10" t="inlineStr">
         <is>
-          <t>16,150</t>
+          <t>16,596</t>
         </is>
       </c>
       <c r="K478" s="10" t="inlineStr">
@@ -46477,7 +46477,7 @@
       </c>
       <c r="P478" s="10" t="inlineStr">
         <is>
-          <t>57,660</t>
+          <t>58,106</t>
         </is>
       </c>
       <c r="Q478" s="10" t="inlineStr">
@@ -46487,12 +46487,12 @@
       </c>
       <c r="R478" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="S478" s="10" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>667</t>
         </is>
       </c>
     </row>
@@ -46504,7 +46504,7 @@
       </c>
       <c r="B479" s="10" t="inlineStr">
         <is>
-          <t>1,159</t>
+          <t>1,163</t>
         </is>
       </c>
       <c r="C479" s="10" t="inlineStr">
@@ -46574,7 +46574,7 @@
       </c>
       <c r="P479" s="10" t="inlineStr">
         <is>
-          <t>8,793</t>
+          <t>8,797</t>
         </is>
       </c>
       <c r="Q479" s="10" t="inlineStr">
@@ -46584,12 +46584,12 @@
       </c>
       <c r="R479" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S479" s="10" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -46601,7 +46601,7 @@
       </c>
       <c r="B480" s="10" t="inlineStr">
         <is>
-          <t>4,427</t>
+          <t>4,430</t>
         </is>
       </c>
       <c r="C480" s="10" t="inlineStr">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="E480" s="10" t="inlineStr">
         <is>
-          <t>82,447</t>
+          <t>82,547</t>
         </is>
       </c>
       <c r="F480" s="10" t="inlineStr">
@@ -46631,7 +46631,7 @@
       </c>
       <c r="H480" s="10" t="inlineStr">
         <is>
-          <t>18,172</t>
+          <t>17,585</t>
         </is>
       </c>
       <c r="I480" s="10" t="inlineStr">
@@ -46671,7 +46671,7 @@
       </c>
       <c r="P480" s="10" t="inlineStr">
         <is>
-          <t>112,927</t>
+          <t>112,443</t>
         </is>
       </c>
       <c r="Q480" s="10" t="inlineStr">
@@ -46681,12 +46681,12 @@
       </c>
       <c r="R480" s="10" t="inlineStr">
         <is>
-          <t>1,784</t>
+          <t>-483</t>
         </is>
       </c>
       <c r="S480" s="10" t="inlineStr">
         <is>
-          <t>14,214</t>
+          <t>13,731</t>
         </is>
       </c>
     </row>
@@ -47295,7 +47295,7 @@
       </c>
       <c r="E487" s="10" t="inlineStr">
         <is>
-          <t>29,988</t>
+          <t>29,488</t>
         </is>
       </c>
       <c r="F487" s="10" t="inlineStr">
@@ -47310,7 +47310,7 @@
       </c>
       <c r="H487" s="10" t="inlineStr">
         <is>
-          <t>55,013</t>
+          <t>57,988</t>
         </is>
       </c>
       <c r="I487" s="10" t="inlineStr">
@@ -47330,7 +47330,7 @@
       </c>
       <c r="L487" s="10" t="inlineStr">
         <is>
-          <t>23,842</t>
+          <t>23,841</t>
         </is>
       </c>
       <c r="M487" s="10" t="inlineStr">
@@ -47350,7 +47350,7 @@
       </c>
       <c r="P487" s="10" t="inlineStr">
         <is>
-          <t>130,221</t>
+          <t>132,695</t>
         </is>
       </c>
       <c r="Q487" s="10" t="inlineStr">
@@ -47360,12 +47360,12 @@
       </c>
       <c r="R487" s="10" t="inlineStr">
         <is>
-          <t>-1,681</t>
+          <t>2,474</t>
         </is>
       </c>
       <c r="S487" s="10" t="inlineStr">
         <is>
-          <t>20,023</t>
+          <t>22,497</t>
         </is>
       </c>
     </row>
@@ -47432,7 +47432,7 @@
       </c>
       <c r="M488" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="N488" s="10" t="inlineStr">
@@ -47447,7 +47447,7 @@
       </c>
       <c r="P488" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="Q488" s="10" t="inlineStr">
@@ -47457,12 +47457,12 @@
       </c>
       <c r="R488" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S488" s="10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -47723,7 +47723,7 @@
       </c>
       <c r="M491" s="10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>336</t>
         </is>
       </c>
       <c r="N491" s="10" t="inlineStr">
@@ -47738,7 +47738,7 @@
       </c>
       <c r="P491" s="10" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
       <c r="Q491" s="10" t="inlineStr">
@@ -47748,12 +47748,12 @@
       </c>
       <c r="R491" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S491" s="10" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -47845,7 +47845,7 @@
       </c>
       <c r="R492" s="10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S492" s="10" t="inlineStr">
@@ -47877,7 +47877,7 @@
       </c>
       <c r="E493" s="10" t="inlineStr">
         <is>
-          <t>46,471</t>
+          <t>46,457</t>
         </is>
       </c>
       <c r="F493" s="10" t="inlineStr">
@@ -47932,7 +47932,7 @@
       </c>
       <c r="P493" s="10" t="inlineStr">
         <is>
-          <t>76,893</t>
+          <t>76,879</t>
         </is>
       </c>
       <c r="Q493" s="10" t="inlineStr">
@@ -47942,12 +47942,12 @@
       </c>
       <c r="R493" s="10" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="S493" s="10" t="inlineStr">
         <is>
-          <t>8,056</t>
+          <t>8,042</t>
         </is>
       </c>
     </row>
@@ -47974,7 +47974,7 @@
       </c>
       <c r="E494" s="10" t="inlineStr">
         <is>
-          <t>3,284</t>
+          <t>3,282</t>
         </is>
       </c>
       <c r="F494" s="10" t="inlineStr">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="P494" s="10" t="inlineStr">
         <is>
-          <t>22,652</t>
+          <t>22,650</t>
         </is>
       </c>
       <c r="Q494" s="10" t="inlineStr">
@@ -48039,12 +48039,12 @@
       </c>
       <c r="R494" s="10" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="S494" s="10" t="inlineStr">
         <is>
-          <t>3,694</t>
+          <t>3,692</t>
         </is>
       </c>
     </row>
@@ -48305,7 +48305,7 @@
       </c>
       <c r="M497" s="10" t="inlineStr">
         <is>
-          <t>1,257</t>
+          <t>1,258</t>
         </is>
       </c>
       <c r="N497" s="10" t="inlineStr">
@@ -48320,7 +48320,7 @@
       </c>
       <c r="P497" s="10" t="inlineStr">
         <is>
-          <t>1,333</t>
+          <t>1,334</t>
         </is>
       </c>
       <c r="Q497" s="10" t="inlineStr">
@@ -48330,12 +48330,12 @@
       </c>
       <c r="R497" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S497" s="10" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
     </row>
@@ -48459,7 +48459,7 @@
       </c>
       <c r="E499" s="10" t="inlineStr">
         <is>
-          <t>50,862</t>
+          <t>50,358</t>
         </is>
       </c>
       <c r="F499" s="10" t="inlineStr">
@@ -48514,7 +48514,7 @@
       </c>
       <c r="P499" s="10" t="inlineStr">
         <is>
-          <t>112,978</t>
+          <t>112,474</t>
         </is>
       </c>
       <c r="Q499" s="10" t="inlineStr">
@@ -48524,12 +48524,12 @@
       </c>
       <c r="R499" s="10" t="inlineStr">
         <is>
-          <t>-735</t>
+          <t>-505</t>
         </is>
       </c>
       <c r="S499" s="10" t="inlineStr">
         <is>
-          <t>3,181</t>
+          <t>2,676</t>
         </is>
       </c>
     </row>
@@ -48663,7 +48663,7 @@
       </c>
       <c r="G501" s="10" t="inlineStr">
         <is>
-          <t>1,023,322</t>
+          <t>1,029,776</t>
         </is>
       </c>
       <c r="H501" s="10" t="inlineStr">
@@ -48708,7 +48708,7 @@
       </c>
       <c r="P501" s="10" t="inlineStr">
         <is>
-          <t>1,107,979</t>
+          <t>1,114,433</t>
         </is>
       </c>
       <c r="Q501" s="10" t="inlineStr">
@@ -48718,12 +48718,12 @@
       </c>
       <c r="R501" s="10" t="inlineStr">
         <is>
-          <t>-2,946</t>
+          <t>6,454</t>
         </is>
       </c>
       <c r="S501" s="10" t="inlineStr">
         <is>
-          <t>230,163</t>
+          <t>236,616</t>
         </is>
       </c>
     </row>
@@ -48735,22 +48735,22 @@
       </c>
       <c r="B502" s="10" t="inlineStr">
         <is>
-          <t>146,414</t>
+          <t>146,878</t>
         </is>
       </c>
       <c r="C502" s="10" t="inlineStr">
         <is>
-          <t>70,136</t>
+          <t>69,854</t>
         </is>
       </c>
       <c r="D502" s="10" t="inlineStr">
         <is>
-          <t>63,515</t>
+          <t>62,528</t>
         </is>
       </c>
       <c r="E502" s="10" t="inlineStr">
         <is>
-          <t>1,179,657</t>
+          <t>1,174,059</t>
         </is>
       </c>
       <c r="F502" s="10" t="inlineStr">
@@ -48760,22 +48760,22 @@
       </c>
       <c r="G502" s="10" t="inlineStr">
         <is>
-          <t>142,957</t>
+          <t>144,754</t>
         </is>
       </c>
       <c r="H502" s="10" t="inlineStr">
         <is>
-          <t>748,129</t>
+          <t>760,070</t>
         </is>
       </c>
       <c r="I502" s="10" t="inlineStr">
         <is>
-          <t>123,763</t>
+          <t>123,268</t>
         </is>
       </c>
       <c r="J502" s="10" t="inlineStr">
         <is>
-          <t>1,021,233</t>
+          <t>1,022,860</t>
         </is>
       </c>
       <c r="K502" s="10" t="inlineStr">
@@ -48785,12 +48785,12 @@
       </c>
       <c r="L502" s="10" t="inlineStr">
         <is>
-          <t>592,176</t>
+          <t>592,283</t>
         </is>
       </c>
       <c r="M502" s="10" t="inlineStr">
         <is>
-          <t>492,526</t>
+          <t>496,133</t>
         </is>
       </c>
       <c r="N502" s="10" t="inlineStr">
@@ -48805,7 +48805,7 @@
       </c>
       <c r="P502" s="10" t="inlineStr">
         <is>
-          <t>4,616,471</t>
+          <t>4,628,651</t>
         </is>
       </c>
       <c r="Q502" s="10" t="inlineStr">
@@ -48815,12 +48815,12 @@
       </c>
       <c r="R502" s="10" t="inlineStr">
         <is>
-          <t>5,602</t>
+          <t>12,180</t>
         </is>
       </c>
       <c r="S502" s="10" t="inlineStr">
         <is>
-          <t>314,187</t>
+          <t>326,366</t>
         </is>
       </c>
     </row>
@@ -49591,7 +49591,7 @@
       </c>
       <c r="R510" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S510" s="10" t="inlineStr">
@@ -50173,7 +50173,7 @@
       </c>
       <c r="R516" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S516" s="10" t="inlineStr">
@@ -50190,22 +50190,22 @@
       </c>
       <c r="B517" s="10" t="inlineStr">
         <is>
-          <t>146,624</t>
+          <t>147,088</t>
         </is>
       </c>
       <c r="C517" s="10" t="inlineStr">
         <is>
-          <t>70,662</t>
+          <t>70,380</t>
         </is>
       </c>
       <c r="D517" s="10" t="inlineStr">
         <is>
-          <t>66,039</t>
+          <t>65,052</t>
         </is>
       </c>
       <c r="E517" s="10" t="inlineStr">
         <is>
-          <t>1,241,713</t>
+          <t>1,236,114</t>
         </is>
       </c>
       <c r="F517" s="10" t="inlineStr">
@@ -50215,22 +50215,22 @@
       </c>
       <c r="G517" s="10" t="inlineStr">
         <is>
-          <t>143,235</t>
+          <t>145,032</t>
         </is>
       </c>
       <c r="H517" s="10" t="inlineStr">
         <is>
-          <t>748,129</t>
+          <t>760,070</t>
         </is>
       </c>
       <c r="I517" s="10" t="inlineStr">
         <is>
-          <t>126,306</t>
+          <t>125,812</t>
         </is>
       </c>
       <c r="J517" s="10" t="inlineStr">
         <is>
-          <t>1,024,573</t>
+          <t>1,026,200</t>
         </is>
       </c>
       <c r="K517" s="10" t="inlineStr">
@@ -50240,12 +50240,12 @@
       </c>
       <c r="L517" s="10" t="inlineStr">
         <is>
-          <t>592,345</t>
+          <t>592,452</t>
         </is>
       </c>
       <c r="M517" s="10" t="inlineStr">
         <is>
-          <t>495,275</t>
+          <t>498,882</t>
         </is>
       </c>
       <c r="N517" s="10" t="inlineStr">
@@ -50260,7 +50260,7 @@
       </c>
       <c r="P517" s="10" t="inlineStr">
         <is>
-          <t>4,690,865</t>
+          <t>4,703,045</t>
         </is>
       </c>
       <c r="Q517" s="10" t="inlineStr">
@@ -50270,12 +50270,12 @@
       </c>
       <c r="R517" s="10" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>12,180</t>
         </is>
       </c>
       <c r="S517" s="10" t="inlineStr">
         <is>
-          <t>318,249</t>
+          <t>330,429</t>
         </is>
       </c>
     </row>
